--- a/InputData/land/BLAPE/cn-BAU LULUCF Anthropogenic Pollutant Emissions.xlsx
+++ b/InputData/land/BLAPE/cn-BAU LULUCF Anthropogenic Pollutant Emissions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\EPS\Github Push\China\eps-china2019-smart-trans\InputData\land\BLAPE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F296BE90-28CB-412F-B1CB-F4B0343B626B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE78FFB-70F2-470A-B544-BD5B71C8E92D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="165" yWindow="2400" windowWidth="21600" windowHeight="11385" tabRatio="833" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="833" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="4" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="827">
   <si>
     <t>单位：万亩</t>
   </si>
@@ -3865,21 +3865,6 @@
   </si>
   <si>
     <r>
-      <t>75</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、2</t>
-    </r>
-    <phoneticPr fontId="27" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <rPr>
         <sz val="10"/>
         <rFont val="Times New Roman"/>
@@ -4074,6 +4059,10 @@
       </rPr>
       <t>其他生物质</t>
     </r>
+  </si>
+  <si>
+    <t>NE</t>
+    <phoneticPr fontId="27" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4086,7 +4075,7 @@
     <numFmt numFmtId="178" formatCode="0_ "/>
     <numFmt numFmtId="179" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4308,12 +4297,6 @@
     <font>
       <sz val="10"/>
       <name val="SimSun"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -5570,11 +5553,11 @@
         <v>336</v>
       </c>
       <c r="B2">
-        <f>温室气体排放清单!K9*10^10</f>
+        <f>温室气体排放清单!N9*10^10</f>
         <v>-1342629000000000</v>
       </c>
       <c r="C2">
-        <f>温室气体排放清单!N9*10^10</f>
+        <f>温室气体排放清单!Q9*10^10</f>
         <v>-1346499000000000</v>
       </c>
       <c r="D2">
@@ -6763,11 +6746,11 @@
         <v>345</v>
       </c>
       <c r="B11">
-        <f>温室气体排放清单!L9*10^10</f>
+        <f>温室气体排放清单!O9*10^10</f>
         <v>1398000000000</v>
       </c>
       <c r="C11">
-        <f>温室气体排放清单!O9*10^10</f>
+        <f>温室气体排放清单!R9*10^10</f>
         <v>1110000000000</v>
       </c>
       <c r="D11">
@@ -11912,42 +11895,47 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2DE32B2-125A-4EC5-B7EE-D8C69A079B2B}">
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="16" width="10" customWidth="1"/>
+    <col min="2" max="19" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:19">
       <c r="A1" s="17"/>
       <c r="B1" s="129">
-        <v>2017</v>
+        <v>2005</v>
       </c>
       <c r="C1" s="129"/>
       <c r="D1" s="129"/>
       <c r="E1" s="129">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="F1" s="129"/>
       <c r="G1" s="129"/>
-      <c r="H1" s="129" t="s">
-        <v>804</v>
+      <c r="H1" s="129">
+        <v>2018</v>
       </c>
       <c r="I1" s="129"/>
       <c r="J1" s="129"/>
       <c r="K1" s="129" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="L1" s="129"/>
       <c r="M1" s="129"/>
-      <c r="N1" s="129">
-        <v>2021</v>
+      <c r="N1" s="129" t="s">
+        <v>805</v>
       </c>
       <c r="O1" s="129"/>
       <c r="P1" s="129"/>
-    </row>
-    <row r="2" spans="1:16" ht="14.25">
+      <c r="Q1" s="129">
+        <v>2021</v>
+      </c>
+      <c r="R1" s="129"/>
+      <c r="S1" s="129"/>
+    </row>
+    <row r="2" spans="1:19" ht="14.25">
       <c r="A2" s="17"/>
       <c r="B2" s="115" t="s">
         <v>806</v>
@@ -11994,567 +11982,674 @@
       <c r="P2" s="115" t="s">
         <v>808</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="14.25">
+      <c r="Q2" s="115" t="s">
+        <v>806</v>
+      </c>
+      <c r="R2" s="115" t="s">
+        <v>807</v>
+      </c>
+      <c r="S2" s="115" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="14.25">
       <c r="A3" s="116" t="s">
         <v>809</v>
       </c>
       <c r="B3" s="117"/>
       <c r="C3" s="117">
-        <v>2470.8000000000002</v>
+        <v>2136.5</v>
       </c>
       <c r="D3" s="117">
-        <v>98.2</v>
+        <v>98.3</v>
       </c>
       <c r="E3" s="117"/>
       <c r="F3" s="117">
-        <v>2136.5</v>
+        <v>2470.8000000000002</v>
       </c>
       <c r="G3" s="117">
-        <v>98.3</v>
+        <v>98.2</v>
       </c>
       <c r="H3" s="117"/>
       <c r="I3" s="117">
-        <v>2384.6</v>
+        <v>2136.5</v>
       </c>
       <c r="J3" s="117">
-        <v>94.3</v>
+        <v>98.3</v>
       </c>
       <c r="K3" s="117"/>
       <c r="L3" s="117">
-        <v>2372</v>
+        <v>2384.6</v>
       </c>
       <c r="M3" s="117">
-        <v>94.6</v>
+        <v>94.3</v>
       </c>
       <c r="N3" s="117"/>
       <c r="O3" s="117">
+        <v>2372</v>
+      </c>
+      <c r="P3" s="117">
+        <v>94.6</v>
+      </c>
+      <c r="Q3" s="117"/>
+      <c r="R3" s="117">
         <v>2427.9</v>
       </c>
-      <c r="P3" s="117">
+      <c r="S3" s="117">
         <v>94.9</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="14.25">
+    <row r="4" spans="1:19" ht="14.25">
       <c r="A4" s="116" t="s">
         <v>810</v>
       </c>
       <c r="B4" s="117"/>
       <c r="C4" s="117">
-        <v>1112.3</v>
+        <v>1120.4000000000001</v>
       </c>
       <c r="D4" s="117"/>
       <c r="E4" s="117"/>
       <c r="F4" s="117">
-        <v>1120.4000000000001</v>
+        <v>1112.3</v>
       </c>
       <c r="G4" s="117"/>
       <c r="H4" s="117"/>
       <c r="I4" s="117">
-        <v>1084.0999999999999</v>
+        <v>1120.4000000000001</v>
       </c>
       <c r="J4" s="117"/>
       <c r="K4" s="117"/>
       <c r="L4" s="117">
-        <v>1124.2</v>
+        <v>1084.0999999999999</v>
       </c>
       <c r="M4" s="117"/>
       <c r="N4" s="117"/>
       <c r="O4" s="117">
+        <v>1124.2</v>
+      </c>
+      <c r="P4" s="117"/>
+      <c r="Q4" s="117"/>
+      <c r="R4" s="117">
         <v>1151.8</v>
       </c>
-      <c r="P4" s="117"/>
-    </row>
-    <row r="5" spans="1:16" ht="14.25">
+      <c r="S4" s="117"/>
+    </row>
+    <row r="5" spans="1:19" ht="14.25">
       <c r="A5" s="116" t="s">
         <v>811</v>
       </c>
       <c r="B5" s="117"/>
       <c r="C5" s="117">
-        <v>354.8</v>
+        <v>240.4</v>
       </c>
       <c r="D5" s="117">
-        <v>22</v>
+        <v>27.2</v>
       </c>
       <c r="E5" s="117"/>
       <c r="F5" s="117">
-        <v>240.4</v>
+        <v>354.8</v>
       </c>
       <c r="G5" s="117">
-        <v>27.2</v>
+        <v>22</v>
       </c>
       <c r="H5" s="117"/>
       <c r="I5" s="117">
-        <v>346.1</v>
+        <v>240.4</v>
       </c>
       <c r="J5" s="117">
-        <v>21.7</v>
+        <v>27.2</v>
       </c>
       <c r="K5" s="117"/>
       <c r="L5" s="117">
-        <v>344.7</v>
+        <v>346.1</v>
       </c>
       <c r="M5" s="117">
-        <v>22.2</v>
+        <v>21.7</v>
       </c>
       <c r="N5" s="117"/>
       <c r="O5" s="117">
+        <v>344.7</v>
+      </c>
+      <c r="P5" s="117">
+        <v>22.2</v>
+      </c>
+      <c r="Q5" s="117"/>
+      <c r="R5" s="117">
         <v>375.3</v>
       </c>
-      <c r="P5" s="117">
+      <c r="S5" s="117">
         <v>22.7</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="14.25">
+    <row r="6" spans="1:19" ht="14.25">
       <c r="A6" s="116" t="s">
         <v>812</v>
       </c>
       <c r="B6" s="117"/>
       <c r="C6" s="117">
-        <v>962.8</v>
+        <v>755</v>
       </c>
       <c r="D6" s="117"/>
       <c r="E6" s="117"/>
       <c r="F6" s="117">
-        <v>755</v>
+        <v>962.8</v>
       </c>
       <c r="G6" s="117"/>
       <c r="H6" s="117"/>
       <c r="I6" s="117">
-        <v>932.9</v>
+        <v>755</v>
       </c>
       <c r="J6" s="117"/>
       <c r="K6" s="117"/>
       <c r="L6" s="117">
-        <v>884.9</v>
+        <v>932.9</v>
       </c>
       <c r="M6" s="117"/>
       <c r="N6" s="117"/>
       <c r="O6" s="117">
+        <v>884.9</v>
+      </c>
+      <c r="P6" s="117"/>
+      <c r="Q6" s="117"/>
+      <c r="R6" s="117">
         <v>885.1</v>
       </c>
-      <c r="P6" s="117"/>
-    </row>
-    <row r="7" spans="1:16" ht="14.25">
+      <c r="S6" s="117"/>
+    </row>
+    <row r="7" spans="1:19" ht="14.25">
       <c r="A7" s="116" t="s">
         <v>813</v>
       </c>
       <c r="B7" s="117"/>
       <c r="C7" s="117"/>
-      <c r="D7" s="117" t="s">
-        <v>814</v>
+      <c r="D7" s="117">
+        <v>70.599999999999994</v>
       </c>
       <c r="E7" s="117"/>
       <c r="F7" s="117"/>
       <c r="G7" s="117">
-        <v>70.599999999999994</v>
+        <v>75.2</v>
       </c>
       <c r="H7" s="117"/>
       <c r="I7" s="117"/>
       <c r="J7" s="117">
-        <v>72</v>
+        <v>70.599999999999994</v>
       </c>
       <c r="K7" s="117"/>
       <c r="L7" s="117"/>
       <c r="M7" s="117">
-        <v>71.900000000000006</v>
+        <v>72</v>
       </c>
       <c r="N7" s="117"/>
       <c r="O7" s="117"/>
       <c r="P7" s="117">
+        <v>71.900000000000006</v>
+      </c>
+      <c r="Q7" s="117"/>
+      <c r="R7" s="117"/>
+      <c r="S7" s="117">
         <v>71.8</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="14.25">
+    <row r="8" spans="1:19" ht="14.25">
       <c r="A8" s="116" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B8" s="117"/>
       <c r="C8" s="117">
-        <v>41</v>
+        <v>20.7</v>
       </c>
       <c r="D8" s="117">
-        <v>1.1000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E8" s="117"/>
       <c r="F8" s="117">
-        <v>20.7</v>
+        <v>41</v>
       </c>
       <c r="G8" s="117">
-        <v>0.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H8" s="117"/>
       <c r="I8" s="117">
-        <v>21.6</v>
+        <v>20.7</v>
       </c>
       <c r="J8" s="117">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K8" s="117"/>
       <c r="L8" s="117">
-        <v>18.2</v>
+        <v>21.6</v>
       </c>
       <c r="M8" s="117">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="N8" s="117"/>
       <c r="O8" s="117">
+        <v>18.2</v>
+      </c>
+      <c r="P8" s="117">
+        <v>0.5</v>
+      </c>
+      <c r="Q8" s="117"/>
+      <c r="R8" s="117">
         <v>15.7</v>
       </c>
-      <c r="P8" s="117">
+      <c r="S8" s="117">
         <v>0.4</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="36.75">
+    <row r="9" spans="1:19" ht="36.75">
       <c r="A9" s="118" t="s">
+        <v>815</v>
+      </c>
+      <c r="B9" s="117">
+        <v>-72866.7</v>
+      </c>
+      <c r="C9" s="117">
+        <v>63.2</v>
+      </c>
+      <c r="D9" s="117">
+        <v>0</v>
+      </c>
+      <c r="E9" s="117">
+        <v>-134171.4</v>
+      </c>
+      <c r="F9" s="117"/>
+      <c r="G9" s="117"/>
+      <c r="H9" s="117">
+        <v>-72866.7</v>
+      </c>
+      <c r="I9" s="117">
+        <v>63.2</v>
+      </c>
+      <c r="J9" s="117">
+        <v>0</v>
+      </c>
+      <c r="K9" s="117">
+        <v>-134047.29999999999</v>
+      </c>
+      <c r="L9" s="117">
+        <v>398.1</v>
+      </c>
+      <c r="M9" s="117">
+        <v>0.1</v>
+      </c>
+      <c r="N9" s="117">
+        <v>-134262.9</v>
+      </c>
+      <c r="O9" s="117">
+        <v>139.80000000000001</v>
+      </c>
+      <c r="P9" s="117">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="117">
+        <v>-134649.9</v>
+      </c>
+      <c r="R9" s="117">
+        <v>111</v>
+      </c>
+      <c r="S9" s="117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="14.25">
+      <c r="A10" s="116" t="s">
         <v>816</v>
       </c>
-      <c r="B9" s="117">
-        <v>-134171.4</v>
-      </c>
-      <c r="C9" s="117"/>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117">
-        <v>-72866.7</v>
-      </c>
-      <c r="F9" s="117">
-        <v>63.2</v>
-      </c>
-      <c r="G9" s="117">
-        <v>0</v>
-      </c>
-      <c r="H9" s="117">
-        <v>-134047.29999999999</v>
-      </c>
-      <c r="I9" s="117">
-        <v>398.1</v>
-      </c>
-      <c r="J9" s="117">
+      <c r="B10" s="117">
+        <v>-55120.5</v>
+      </c>
+      <c r="C10" s="117">
+        <v>0.2</v>
+      </c>
+      <c r="D10" s="117">
+        <v>0</v>
+      </c>
+      <c r="E10" s="117">
+        <v>-92842</v>
+      </c>
+      <c r="F10" s="117"/>
+      <c r="G10" s="117"/>
+      <c r="H10" s="117">
+        <v>-55120.5</v>
+      </c>
+      <c r="I10" s="117">
+        <v>0.2</v>
+      </c>
+      <c r="J10" s="117">
+        <v>0</v>
+      </c>
+      <c r="K10" s="117">
+        <v>-96579.199999999997</v>
+      </c>
+      <c r="L10" s="117">
         <v>0.1</v>
       </c>
-      <c r="K9" s="117">
-        <v>-134262.9</v>
-      </c>
-      <c r="L9" s="117">
-        <v>139.80000000000001</v>
-      </c>
-      <c r="M9" s="117">
-        <v>0</v>
-      </c>
-      <c r="N9" s="117">
-        <v>-134649.9</v>
-      </c>
-      <c r="O9" s="117">
-        <v>111</v>
-      </c>
-      <c r="P9" s="117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="14.25">
-      <c r="A10" s="116" t="s">
+      <c r="M10" s="117">
+        <v>0</v>
+      </c>
+      <c r="N10" s="117">
+        <v>-89559.2</v>
+      </c>
+      <c r="O10" s="117">
+        <v>0</v>
+      </c>
+      <c r="P10" s="117">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="117">
+        <v>-87682.7</v>
+      </c>
+      <c r="R10" s="117">
+        <v>0</v>
+      </c>
+      <c r="S10" s="117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="14.25">
+      <c r="A11" s="116" t="s">
         <v>817</v>
       </c>
-      <c r="B10" s="117">
-        <v>-92842</v>
-      </c>
-      <c r="C10" s="117"/>
-      <c r="D10" s="117"/>
-      <c r="E10" s="117">
-        <v>-55120.5</v>
-      </c>
-      <c r="F10" s="117">
-        <v>0.2</v>
-      </c>
-      <c r="G10" s="117">
-        <v>0</v>
-      </c>
-      <c r="H10" s="117">
-        <v>-96579.199999999997</v>
-      </c>
-      <c r="I10" s="117">
-        <v>0.1</v>
-      </c>
-      <c r="J10" s="117">
-        <v>0</v>
-      </c>
-      <c r="K10" s="117">
-        <v>-89559.2</v>
-      </c>
-      <c r="L10" s="117">
-        <v>0</v>
-      </c>
-      <c r="M10" s="117">
-        <v>0</v>
-      </c>
-      <c r="N10" s="117">
-        <v>-87682.7</v>
-      </c>
-      <c r="O10" s="117">
-        <v>0</v>
-      </c>
-      <c r="P10" s="117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="14.25">
-      <c r="A11" s="116" t="s">
-        <v>818</v>
-      </c>
       <c r="B11" s="117">
-        <v>-9643.2999999999993</v>
+        <v>-4107.7</v>
       </c>
       <c r="C11" s="117"/>
       <c r="D11" s="117"/>
       <c r="E11" s="117">
-        <v>-4107.7</v>
+        <v>-9643.2999999999993</v>
       </c>
       <c r="F11" s="117"/>
       <c r="G11" s="117"/>
       <c r="H11" s="117">
+        <v>-4107.7</v>
+      </c>
+      <c r="I11" s="117"/>
+      <c r="J11" s="117"/>
+      <c r="K11" s="117">
         <v>-7810</v>
       </c>
-      <c r="I11" s="117" t="s">
-        <v>819</v>
-      </c>
-      <c r="J11" s="117" t="s">
-        <v>819</v>
-      </c>
-      <c r="K11" s="117">
+      <c r="L11" s="117" t="s">
+        <v>818</v>
+      </c>
+      <c r="M11" s="117" t="s">
+        <v>818</v>
+      </c>
+      <c r="N11" s="117">
         <v>-9801.7999999999993</v>
-      </c>
-      <c r="L11" s="117"/>
-      <c r="M11" s="117"/>
-      <c r="N11" s="117">
-        <v>-10616.2</v>
       </c>
       <c r="O11" s="117"/>
       <c r="P11" s="117"/>
-    </row>
-    <row r="12" spans="1:16" ht="14.25">
+      <c r="Q11" s="117">
+        <v>-10616.2</v>
+      </c>
+      <c r="R11" s="117"/>
+      <c r="S11" s="117"/>
+    </row>
+    <row r="12" spans="1:19" ht="14.25">
       <c r="A12" s="116" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B12" s="117">
-        <v>-12101.3</v>
+        <v>-4776.8999999999996</v>
       </c>
       <c r="C12" s="117">
         <v>0.1</v>
       </c>
       <c r="D12" s="117">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="117">
-        <v>-4776.8999999999996</v>
+        <v>-12101.3</v>
       </c>
       <c r="F12" s="117">
         <v>0.1</v>
       </c>
       <c r="G12" s="117">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H12" s="117">
-        <v>-10175.200000000001</v>
+        <v>-4776.8999999999996</v>
       </c>
       <c r="I12" s="117">
         <v>0.1</v>
       </c>
       <c r="J12" s="117">
+        <v>0</v>
+      </c>
+      <c r="K12" s="117">
+        <v>-10175.200000000001</v>
+      </c>
+      <c r="L12" s="117">
         <v>0.1</v>
       </c>
-      <c r="K12" s="117">
+      <c r="M12" s="117">
+        <v>0.1</v>
+      </c>
+      <c r="N12" s="117">
         <v>-7270.7</v>
       </c>
-      <c r="L12" s="117">
-        <v>0</v>
-      </c>
-      <c r="M12" s="117">
-        <v>0</v>
-      </c>
-      <c r="N12" s="117">
+      <c r="O12" s="117">
+        <v>0</v>
+      </c>
+      <c r="P12" s="117">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="117">
         <v>-6408.2</v>
       </c>
-      <c r="O12" s="117">
-        <v>0</v>
-      </c>
-      <c r="P12" s="117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="14.25">
+      <c r="R12" s="117">
+        <v>0</v>
+      </c>
+      <c r="S12" s="117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="14.25">
       <c r="A13" s="116" t="s">
+        <v>820</v>
+      </c>
+      <c r="B13" s="117">
+        <v>-1373</v>
+      </c>
+      <c r="C13" s="117">
+        <v>62.9</v>
+      </c>
+      <c r="D13" s="117" t="s">
+        <v>826</v>
+      </c>
+      <c r="E13" s="117">
+        <v>-8586.2999999999993</v>
+      </c>
+      <c r="F13" s="117">
+        <v>398.3</v>
+      </c>
+      <c r="G13" s="117"/>
+      <c r="H13" s="117">
+        <v>-1373</v>
+      </c>
+      <c r="I13" s="117">
+        <v>62.9</v>
+      </c>
+      <c r="J13" s="117" t="s">
         <v>821</v>
       </c>
-      <c r="B13" s="117">
-        <v>-8586.2999999999993</v>
-      </c>
-      <c r="C13" s="117">
-        <v>398.3</v>
-      </c>
-      <c r="D13" s="117"/>
-      <c r="E13" s="117">
-        <v>-1373</v>
-      </c>
-      <c r="F13" s="117">
-        <v>62.9</v>
-      </c>
-      <c r="G13" s="117" t="s">
+      <c r="K13" s="117">
+        <v>-8641.7000000000007</v>
+      </c>
+      <c r="L13" s="117">
+        <v>398</v>
+      </c>
+      <c r="M13" s="117" t="s">
+        <v>821</v>
+      </c>
+      <c r="N13" s="117">
+        <v>-2978.8</v>
+      </c>
+      <c r="O13" s="117">
+        <v>139.80000000000001</v>
+      </c>
+      <c r="P13" s="117" t="s">
+        <v>821</v>
+      </c>
+      <c r="Q13" s="117">
+        <v>-2459.9</v>
+      </c>
+      <c r="R13" s="117">
+        <v>111</v>
+      </c>
+      <c r="S13" s="117" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="14.25">
+      <c r="A14" s="116" t="s">
         <v>822</v>
       </c>
-      <c r="H13" s="117">
-        <v>-8641.7000000000007</v>
-      </c>
-      <c r="I13" s="117">
-        <v>398</v>
-      </c>
-      <c r="J13" s="117" t="s">
-        <v>822</v>
-      </c>
-      <c r="K13" s="117">
-        <v>-2978.8</v>
-      </c>
-      <c r="L13" s="117">
-        <v>139.80000000000001</v>
-      </c>
-      <c r="M13" s="117" t="s">
-        <v>822</v>
-      </c>
-      <c r="N13" s="117">
-        <v>-2459.9</v>
-      </c>
-      <c r="O13" s="117">
-        <v>111</v>
-      </c>
-      <c r="P13" s="117" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="14.25">
-      <c r="A14" s="116" t="s">
-        <v>823</v>
-      </c>
       <c r="B14" s="117">
-        <v>-102.8</v>
+        <v>16.3</v>
       </c>
       <c r="C14" s="117"/>
       <c r="D14" s="117"/>
       <c r="E14" s="117">
-        <v>16.3</v>
+        <v>-102.8</v>
       </c>
       <c r="F14" s="117"/>
       <c r="G14" s="117"/>
       <c r="H14" s="117">
-        <v>-91.8</v>
+        <v>16.3</v>
       </c>
       <c r="I14" s="117"/>
       <c r="J14" s="117"/>
       <c r="K14" s="117">
-        <v>-239.6</v>
+        <v>-91.8</v>
       </c>
       <c r="L14" s="117"/>
       <c r="M14" s="117"/>
       <c r="N14" s="117">
-        <v>-63.4</v>
+        <v>-239.6</v>
       </c>
       <c r="O14" s="117"/>
       <c r="P14" s="117"/>
-    </row>
-    <row r="15" spans="1:16" ht="14.25">
+      <c r="Q14" s="117">
+        <v>-63.4</v>
+      </c>
+      <c r="R14" s="117"/>
+      <c r="S14" s="117"/>
+    </row>
+    <row r="15" spans="1:19" ht="14.25">
       <c r="A15" s="116" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B15" s="117">
-        <v>118.3</v>
+        <v>543.6</v>
       </c>
       <c r="C15" s="117"/>
       <c r="D15" s="117"/>
       <c r="E15" s="117">
-        <v>543.6</v>
+        <v>118.3</v>
       </c>
       <c r="F15" s="117"/>
       <c r="G15" s="117"/>
       <c r="H15" s="117">
-        <v>109.5</v>
+        <v>543.6</v>
       </c>
       <c r="I15" s="117"/>
       <c r="J15" s="117"/>
       <c r="K15" s="117">
-        <v>264.10000000000002</v>
+        <v>109.5</v>
       </c>
       <c r="L15" s="117"/>
       <c r="M15" s="117"/>
       <c r="N15" s="117">
-        <v>155.6</v>
+        <v>264.10000000000002</v>
       </c>
       <c r="O15" s="117"/>
       <c r="P15" s="117"/>
-    </row>
-    <row r="16" spans="1:16" ht="14.25">
+      <c r="Q15" s="117">
+        <v>155.6</v>
+      </c>
+      <c r="R15" s="117"/>
+      <c r="S15" s="117"/>
+    </row>
+    <row r="16" spans="1:19" ht="14.25">
       <c r="A16" s="116" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B16" s="117">
-        <v>-11014</v>
+        <v>-6121.5</v>
       </c>
       <c r="C16" s="117"/>
       <c r="D16" s="117"/>
       <c r="E16" s="117">
-        <v>-6121.5</v>
+        <v>-11014</v>
       </c>
       <c r="F16" s="117"/>
       <c r="G16" s="117"/>
       <c r="H16" s="117">
-        <v>-10859</v>
+        <v>-6121.5</v>
       </c>
       <c r="I16" s="117"/>
       <c r="J16" s="117"/>
       <c r="K16" s="117">
-        <v>-10386.299999999999</v>
+        <v>-10859</v>
       </c>
       <c r="L16" s="117"/>
       <c r="M16" s="117"/>
       <c r="N16" s="117">
-        <v>-10382</v>
+        <v>-10386.299999999999</v>
       </c>
       <c r="O16" s="117"/>
       <c r="P16" s="117"/>
-    </row>
-    <row r="17" spans="1:16" ht="14.25">
+      <c r="Q16" s="117">
+        <v>-10382</v>
+      </c>
+      <c r="R16" s="117"/>
+      <c r="S16" s="117"/>
+    </row>
+    <row r="17" spans="1:19" ht="14.25">
       <c r="A17" s="116" t="s">
-        <v>826</v>
-      </c>
-      <c r="B17" s="117"/>
+        <v>825</v>
+      </c>
+      <c r="B17" s="117">
+        <v>-1927.1</v>
+      </c>
       <c r="C17" s="117"/>
       <c r="D17" s="117"/>
-      <c r="E17" s="117">
-        <v>-1927.1</v>
-      </c>
+      <c r="E17" s="117"/>
       <c r="F17" s="117"/>
       <c r="G17" s="117"/>
-      <c r="H17" s="117"/>
+      <c r="H17" s="117">
+        <v>-1927.1</v>
+      </c>
       <c r="I17" s="117"/>
       <c r="J17" s="117"/>
-      <c r="K17" s="117">
-        <v>-14290.6</v>
-      </c>
+      <c r="K17" s="117"/>
       <c r="L17" s="117"/>
       <c r="M17" s="117"/>
       <c r="N17" s="117">
-        <v>-17193.099999999999</v>
+        <v>-14290.6</v>
       </c>
       <c r="O17" s="117"/>
       <c r="P17" s="117"/>
+      <c r="Q17" s="117">
+        <v>-17193.099999999999</v>
+      </c>
+      <c r="R17" s="117"/>
+      <c r="S17" s="117"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="K1:M1"/>
     <mergeCell ref="N1:P1"/>
+    <mergeCell ref="Q1:S1"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
-  <conditionalFormatting sqref="B3:P17">
+  <conditionalFormatting sqref="B3:S17">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/InputData/land/BLAPE/cn-BAU LULUCF Anthropogenic Pollutant Emissions.xlsx
+++ b/InputData/land/BLAPE/cn-BAU LULUCF Anthropogenic Pollutant Emissions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\EPS\Github Push\China\eps-china2019-smart-trans\InputData\land\BLAPE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE78FFB-70F2-470A-B544-BD5B71C8E92D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935CB4C9-CED1-4FCF-A3EF-029DB916D04C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="833" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="833" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="4" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="826">
   <si>
     <t>单位：万亩</t>
   </si>
@@ -3684,10 +3684,6 @@
   <si>
     <t>Territorial Ecological Restoration Plan of Shandong Province (2021-2035)</t>
     <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
-    <t>2020a</t>
-    <phoneticPr fontId="27" type="noConversion"/>
   </si>
   <si>
     <t>2020b</t>
@@ -6915,168 +6911,167 @@
         <v>346</v>
       </c>
       <c r="B12">
-        <f>-'data from RPEPUACE'!B12*B2</f>
-        <v>51730616198.787018</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <f>-'data from RPEPUACE'!B12*C2</f>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!B12*(C2-$B2)+B12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="D12">
-        <f>C12</f>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!C12*(D2-$B2)+C12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="E12">
-        <f t="shared" ref="E12:AP12" si="2">D12</f>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!D12*(E2-$B2)+D12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="F12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!E12*(F2-$B2)+E12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="G12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!F12*(G2-$B2)+F12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="H12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!G12*(H2-$B2)+G12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="I12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!H12*(I2-$B2)+H12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="J12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!I12*(J2-$B2)+I12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="K12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!J12*(K2-$B2)+J12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="L12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!K12*(L2-$B2)+K12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="M12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!L12*(M2-$B2)+L12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="N12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!M12*(N2-$B2)+M12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="O12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!N12*(O2-$B2)+N12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="P12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!O12*(P2-$B2)+O12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!P12*(Q2-$B2)+P12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="R12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!Q12*(R2-$B2)+Q12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="S12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!R12*(S2-$B2)+R12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="T12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!S12*(T2-$B2)+S12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="U12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!T12*(U2-$B2)+T12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="V12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!U12*(V2-$B2)+U12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="W12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!V12*(W2-$B2)+V12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="X12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!W12*(X2-$B2)+W12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!X12*(Y2-$B2)+X12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="Z12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!Y12*(Z2-$B2)+Y12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="AA12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!Z12*(AA2-$B2)+Z12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="AB12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!AA12*(AB2-$B2)+AA12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="AC12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!AB12*(AC2-$B2)+AB12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="AD12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!AC12*(AD2-$B2)+AC12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="AE12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!AD12*(AE2-$B2)+AD12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="AF12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!AE12*(AF2-$B2)+AE12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="AG12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!AF12*(AG2-$B2)+AF12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="AH12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!AG12*(AH2-$B2)+AG12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="AI12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!AH12*(AI2-$B2)+AH12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="AJ12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!AI12*(AJ2-$B2)+AI12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="AK12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!AJ12*(AK2-$B2)+AJ12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="AL12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!AK12*(AL2-$B2)+AK12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="AM12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!AL12*(AM2-$B2)+AL12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="AN12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!AM12*(AN2-$B2)+AM12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="AO12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!AN12*(AO2-$B2)+AN12</f>
+        <v>149108565.87285522</v>
       </c>
       <c r="AP12">
-        <f t="shared" si="2"/>
-        <v>51879724764.659866</v>
+        <f>-'data from RPEPUACE'!AO12*(AP2-$B2)+AO12</f>
+        <v>149108565.87285522</v>
       </c>
     </row>
     <row r="13" spans="1:42">
@@ -11910,22 +11905,22 @@
       <c r="C1" s="129"/>
       <c r="D1" s="129"/>
       <c r="E1" s="129">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="F1" s="129"/>
       <c r="G1" s="129"/>
       <c r="H1" s="129">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="I1" s="129"/>
       <c r="J1" s="129"/>
-      <c r="K1" s="129" t="s">
-        <v>804</v>
+      <c r="K1" s="129">
+        <v>2018</v>
       </c>
       <c r="L1" s="129"/>
       <c r="M1" s="129"/>
       <c r="N1" s="129" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="O1" s="129"/>
       <c r="P1" s="129"/>
@@ -11938,63 +11933,63 @@
     <row r="2" spans="1:19" ht="14.25">
       <c r="A2" s="17"/>
       <c r="B2" s="115" t="s">
+        <v>805</v>
+      </c>
+      <c r="C2" s="115" t="s">
         <v>806</v>
       </c>
-      <c r="C2" s="115" t="s">
+      <c r="D2" s="115" t="s">
         <v>807</v>
       </c>
-      <c r="D2" s="115" t="s">
-        <v>808</v>
-      </c>
       <c r="E2" s="115" t="s">
+        <v>805</v>
+      </c>
+      <c r="F2" s="115" t="s">
         <v>806</v>
       </c>
-      <c r="F2" s="115" t="s">
+      <c r="G2" s="115" t="s">
         <v>807</v>
       </c>
-      <c r="G2" s="115" t="s">
-        <v>808</v>
-      </c>
       <c r="H2" s="115" t="s">
+        <v>805</v>
+      </c>
+      <c r="I2" s="115" t="s">
         <v>806</v>
       </c>
-      <c r="I2" s="115" t="s">
+      <c r="J2" s="115" t="s">
         <v>807</v>
       </c>
-      <c r="J2" s="115" t="s">
-        <v>808</v>
-      </c>
       <c r="K2" s="115" t="s">
+        <v>805</v>
+      </c>
+      <c r="L2" s="115" t="s">
         <v>806</v>
       </c>
-      <c r="L2" s="115" t="s">
+      <c r="M2" s="115" t="s">
         <v>807</v>
       </c>
-      <c r="M2" s="115" t="s">
-        <v>808</v>
-      </c>
       <c r="N2" s="115" t="s">
+        <v>805</v>
+      </c>
+      <c r="O2" s="115" t="s">
         <v>806</v>
       </c>
-      <c r="O2" s="115" t="s">
+      <c r="P2" s="115" t="s">
         <v>807</v>
       </c>
-      <c r="P2" s="115" t="s">
-        <v>808</v>
-      </c>
       <c r="Q2" s="115" t="s">
+        <v>805</v>
+      </c>
+      <c r="R2" s="115" t="s">
         <v>806</v>
       </c>
-      <c r="R2" s="115" t="s">
+      <c r="S2" s="115" t="s">
         <v>807</v>
-      </c>
-      <c r="S2" s="115" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="14.25">
       <c r="A3" s="116" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B3" s="117"/>
       <c r="C3" s="117">
@@ -12005,17 +12000,17 @@
       </c>
       <c r="E3" s="117"/>
       <c r="F3" s="117">
-        <v>2470.8000000000002</v>
+        <v>2241.4</v>
       </c>
       <c r="G3" s="117">
-        <v>98.2</v>
+        <v>115.4</v>
       </c>
       <c r="H3" s="117"/>
       <c r="I3" s="117">
-        <v>2136.5</v>
+        <v>2470.8000000000002</v>
       </c>
       <c r="J3" s="117">
-        <v>98.3</v>
+        <v>98.2</v>
       </c>
       <c r="K3" s="117"/>
       <c r="L3" s="117">
@@ -12041,7 +12036,7 @@
     </row>
     <row r="4" spans="1:19" ht="14.25">
       <c r="A4" s="116" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B4" s="117"/>
       <c r="C4" s="117">
@@ -12050,12 +12045,12 @@
       <c r="D4" s="117"/>
       <c r="E4" s="117"/>
       <c r="F4" s="117">
-        <v>1112.3</v>
+        <v>1032.9000000000001</v>
       </c>
       <c r="G4" s="117"/>
       <c r="H4" s="117"/>
       <c r="I4" s="117">
-        <v>1120.4000000000001</v>
+        <v>1112.3</v>
       </c>
       <c r="J4" s="117"/>
       <c r="K4" s="117"/>
@@ -12076,7 +12071,7 @@
     </row>
     <row r="5" spans="1:19" ht="14.25">
       <c r="A5" s="116" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B5" s="117"/>
       <c r="C5" s="117">
@@ -12087,17 +12082,17 @@
       </c>
       <c r="E5" s="117"/>
       <c r="F5" s="117">
-        <v>354.8</v>
+        <v>304.8</v>
       </c>
       <c r="G5" s="117">
-        <v>22</v>
+        <v>23.6</v>
       </c>
       <c r="H5" s="117"/>
       <c r="I5" s="117">
-        <v>240.4</v>
+        <v>354.8</v>
       </c>
       <c r="J5" s="117">
-        <v>27.2</v>
+        <v>22</v>
       </c>
       <c r="K5" s="117"/>
       <c r="L5" s="117">
@@ -12123,7 +12118,7 @@
     </row>
     <row r="6" spans="1:19" ht="14.25">
       <c r="A6" s="116" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B6" s="117"/>
       <c r="C6" s="117">
@@ -12132,12 +12127,12 @@
       <c r="D6" s="117"/>
       <c r="E6" s="117"/>
       <c r="F6" s="117">
-        <v>962.8</v>
+        <v>872.9</v>
       </c>
       <c r="G6" s="117"/>
       <c r="H6" s="117"/>
       <c r="I6" s="117">
-        <v>755</v>
+        <v>962.8</v>
       </c>
       <c r="J6" s="117"/>
       <c r="K6" s="117"/>
@@ -12158,7 +12153,7 @@
     </row>
     <row r="7" spans="1:19" ht="14.25">
       <c r="A7" s="116" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B7" s="117"/>
       <c r="C7" s="117"/>
@@ -12168,12 +12163,12 @@
       <c r="E7" s="117"/>
       <c r="F7" s="117"/>
       <c r="G7" s="117">
-        <v>75.2</v>
+        <v>91.1</v>
       </c>
       <c r="H7" s="117"/>
       <c r="I7" s="117"/>
       <c r="J7" s="117">
-        <v>70.599999999999994</v>
+        <v>75.2</v>
       </c>
       <c r="K7" s="117"/>
       <c r="L7" s="117"/>
@@ -12193,7 +12188,7 @@
     </row>
     <row r="8" spans="1:19" ht="14.25">
       <c r="A8" s="116" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B8" s="117"/>
       <c r="C8" s="117">
@@ -12204,17 +12199,17 @@
       </c>
       <c r="E8" s="117"/>
       <c r="F8" s="117">
-        <v>41</v>
+        <v>30.7</v>
       </c>
       <c r="G8" s="117">
-        <v>1.1000000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="H8" s="117"/>
       <c r="I8" s="117">
-        <v>20.7</v>
+        <v>41</v>
       </c>
       <c r="J8" s="117">
-        <v>0.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K8" s="117"/>
       <c r="L8" s="117">
@@ -12240,7 +12235,7 @@
     </row>
     <row r="9" spans="1:19" ht="36.75">
       <c r="A9" s="118" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B9" s="117">
         <v>-72866.7</v>
@@ -12252,19 +12247,19 @@
         <v>0</v>
       </c>
       <c r="E9" s="117">
+        <v>-102972</v>
+      </c>
+      <c r="F9" s="117">
+        <v>174</v>
+      </c>
+      <c r="G9" s="117">
+        <v>0.1</v>
+      </c>
+      <c r="H9" s="117">
         <v>-134171.4</v>
       </c>
-      <c r="F9" s="117"/>
-      <c r="G9" s="117"/>
-      <c r="H9" s="117">
-        <v>-72866.7</v>
-      </c>
-      <c r="I9" s="117">
-        <v>63.2</v>
-      </c>
-      <c r="J9" s="117">
-        <v>0</v>
-      </c>
+      <c r="I9" s="117"/>
+      <c r="J9" s="117"/>
       <c r="K9" s="117">
         <v>-134047.29999999999</v>
       </c>
@@ -12295,7 +12290,7 @@
     </row>
     <row r="10" spans="1:19" ht="14.25">
       <c r="A10" s="116" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B10" s="117">
         <v>-55120.5</v>
@@ -12307,19 +12302,19 @@
         <v>0</v>
       </c>
       <c r="E10" s="117">
+        <v>-77923</v>
+      </c>
+      <c r="F10" s="117">
+        <v>0.1</v>
+      </c>
+      <c r="G10" s="117">
+        <v>0</v>
+      </c>
+      <c r="H10" s="117">
         <v>-92842</v>
       </c>
-      <c r="F10" s="117"/>
-      <c r="G10" s="117"/>
-      <c r="H10" s="117">
-        <v>-55120.5</v>
-      </c>
-      <c r="I10" s="117">
-        <v>0.2</v>
-      </c>
-      <c r="J10" s="117">
-        <v>0</v>
-      </c>
+      <c r="I10" s="117"/>
+      <c r="J10" s="117"/>
       <c r="K10" s="117">
         <v>-96579.199999999997</v>
       </c>
@@ -12350,7 +12345,7 @@
     </row>
     <row r="11" spans="1:19" ht="14.25">
       <c r="A11" s="116" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B11" s="117">
         <v>-4107.7</v>
@@ -12358,12 +12353,16 @@
       <c r="C11" s="117"/>
       <c r="D11" s="117"/>
       <c r="E11" s="117">
+        <v>-6604</v>
+      </c>
+      <c r="F11" s="117" t="s">
+        <v>817</v>
+      </c>
+      <c r="G11" s="117" t="s">
+        <v>817</v>
+      </c>
+      <c r="H11" s="117">
         <v>-9643.2999999999993</v>
-      </c>
-      <c r="F11" s="117"/>
-      <c r="G11" s="117"/>
-      <c r="H11" s="117">
-        <v>-4107.7</v>
       </c>
       <c r="I11" s="117"/>
       <c r="J11" s="117"/>
@@ -12371,10 +12370,10 @@
         <v>-7810</v>
       </c>
       <c r="L11" s="117" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="M11" s="117" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="N11" s="117">
         <v>-9801.7999999999993</v>
@@ -12389,7 +12388,7 @@
     </row>
     <row r="12" spans="1:19" ht="14.25">
       <c r="A12" s="116" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B12" s="117">
         <v>-4776.8999999999996</v>
@@ -12401,7 +12400,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="117">
-        <v>-12101.3</v>
+        <v>-4513</v>
       </c>
       <c r="F12" s="117">
         <v>0.1</v>
@@ -12410,13 +12409,13 @@
         <v>0.1</v>
       </c>
       <c r="H12" s="117">
-        <v>-4776.8999999999996</v>
+        <v>-12101.3</v>
       </c>
       <c r="I12" s="117">
         <v>0.1</v>
       </c>
       <c r="J12" s="117">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K12" s="117">
         <v>-10175.200000000001</v>
@@ -12448,7 +12447,7 @@
     </row>
     <row r="13" spans="1:19" ht="14.25">
       <c r="A13" s="116" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B13" s="117">
         <v>-1373</v>
@@ -12457,24 +12456,24 @@
         <v>62.9</v>
       </c>
       <c r="D13" s="117" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="E13" s="117">
+        <v>-4508</v>
+      </c>
+      <c r="F13" s="117">
+        <v>174</v>
+      </c>
+      <c r="G13" s="117" t="s">
+        <v>820</v>
+      </c>
+      <c r="H13" s="117">
         <v>-8586.2999999999993</v>
       </c>
-      <c r="F13" s="117">
+      <c r="I13" s="117">
         <v>398.3</v>
       </c>
-      <c r="G13" s="117"/>
-      <c r="H13" s="117">
-        <v>-1373</v>
-      </c>
-      <c r="I13" s="117">
-        <v>62.9</v>
-      </c>
-      <c r="J13" s="117" t="s">
-        <v>821</v>
-      </c>
+      <c r="J13" s="117"/>
       <c r="K13" s="117">
         <v>-8641.7000000000007</v>
       </c>
@@ -12482,7 +12481,7 @@
         <v>398</v>
       </c>
       <c r="M13" s="117" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="N13" s="117">
         <v>-2978.8</v>
@@ -12491,7 +12490,7 @@
         <v>139.80000000000001</v>
       </c>
       <c r="P13" s="117" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="Q13" s="117">
         <v>-2459.9</v>
@@ -12500,12 +12499,12 @@
         <v>111</v>
       </c>
       <c r="S13" s="117" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="14.25">
       <c r="A14" s="116" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B14" s="117">
         <v>16.3</v>
@@ -12513,12 +12512,12 @@
       <c r="C14" s="117"/>
       <c r="D14" s="117"/>
       <c r="E14" s="117">
-        <v>-102.8</v>
+        <v>162</v>
       </c>
       <c r="F14" s="117"/>
       <c r="G14" s="117"/>
       <c r="H14" s="117">
-        <v>16.3</v>
+        <v>-102.8</v>
       </c>
       <c r="I14" s="117"/>
       <c r="J14" s="117"/>
@@ -12540,7 +12539,7 @@
     </row>
     <row r="15" spans="1:19" ht="14.25">
       <c r="A15" s="116" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B15" s="117">
         <v>543.6</v>
@@ -12548,12 +12547,12 @@
       <c r="C15" s="117"/>
       <c r="D15" s="117"/>
       <c r="E15" s="117">
-        <v>118.3</v>
+        <v>0</v>
       </c>
       <c r="F15" s="117"/>
       <c r="G15" s="117"/>
       <c r="H15" s="117">
-        <v>543.6</v>
+        <v>118.3</v>
       </c>
       <c r="I15" s="117"/>
       <c r="J15" s="117"/>
@@ -12575,7 +12574,7 @@
     </row>
     <row r="16" spans="1:19" ht="14.25">
       <c r="A16" s="116" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B16" s="117">
         <v>-6121.5</v>
@@ -12583,12 +12582,12 @@
       <c r="C16" s="117"/>
       <c r="D16" s="117"/>
       <c r="E16" s="117">
-        <v>-11014</v>
+        <v>-9586</v>
       </c>
       <c r="F16" s="117"/>
       <c r="G16" s="117"/>
       <c r="H16" s="117">
-        <v>-6121.5</v>
+        <v>-11014</v>
       </c>
       <c r="I16" s="117"/>
       <c r="J16" s="117"/>
@@ -12610,7 +12609,7 @@
     </row>
     <row r="17" spans="1:19" ht="14.25">
       <c r="A17" s="116" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B17" s="117">
         <v>-1927.1</v>
@@ -12620,9 +12619,7 @@
       <c r="E17" s="117"/>
       <c r="F17" s="117"/>
       <c r="G17" s="117"/>
-      <c r="H17" s="117">
-        <v>-1927.1</v>
-      </c>
+      <c r="H17" s="117"/>
       <c r="I17" s="117"/>
       <c r="J17" s="117"/>
       <c r="K17" s="117"/>
@@ -12641,12 +12638,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="Q1:S1"/>
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:G1"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="K1:M1"/>
+    <mergeCell ref="E1:G1"/>
     <mergeCell ref="N1:P1"/>
-    <mergeCell ref="Q1:S1"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <conditionalFormatting sqref="B3:S17">

--- a/InputData/land/BLAPE/cn-BAU LULUCF Anthropogenic Pollutant Emissions.xlsx
+++ b/InputData/land/BLAPE/cn-BAU LULUCF Anthropogenic Pollutant Emissions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\EPS\Github Push\China\eps-china2019-smart-trans\InputData\land\BLAPE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935CB4C9-CED1-4FCF-A3EF-029DB916D04C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAFD256B-05E4-4F93-B78C-664F6E23D491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="833" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="833" firstSheet="3" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="4" r:id="rId1"/>
@@ -22,7 +22,8 @@
     <sheet name="2021 Forestry Product" sheetId="8" r:id="rId7"/>
     <sheet name="2019 Regional CO2 LAPE" sheetId="7" r:id="rId8"/>
     <sheet name="data from RPEPUACE" sheetId="2" r:id="rId9"/>
-    <sheet name="BLAPE" sheetId="3" r:id="rId10"/>
+    <sheet name="Policy Action" sheetId="12" r:id="rId10"/>
+    <sheet name="BLAPE" sheetId="3" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="839">
   <si>
     <t>单位：万亩</t>
   </si>
@@ -4060,6 +4061,45 @@
     <t>NE</t>
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
+  <si>
+    <t>Time (Year)</t>
+  </si>
+  <si>
+    <t>Change in LULUCF Emissions[CO2] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Change in LULUCF Emissions[VOC] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Change in LULUCF Emissions[CO] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Change in LULUCF Emissions[NOx] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Change in LULUCF Emissions[PM10] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Change in LULUCF Emissions[PM25] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Change in LULUCF Emissions[SOx] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Change in LULUCF Emissions[BC] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Change in LULUCF Emissions[OC] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Change in LULUCF Emissions[CH4] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Change in LULUCF Emissions[N2O] : MostRecentRun</t>
+  </si>
+  <si>
+    <t>Change in LULUCF Emissions[F gases] : MostRecentRun</t>
+  </si>
 </sst>
 </file>
 
@@ -4071,7 +4111,7 @@
     <numFmt numFmtId="178" formatCode="0_ "/>
     <numFmt numFmtId="179" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4294,6 +4334,12 @@
       <sz val="10"/>
       <name val="SimSun"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="12">
@@ -4638,7 +4684,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5028,6 +5074,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="20% - 着色 5" xfId="1" builtinId="46"/>
@@ -5405,6 +5454,1834 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F93ED2C9-C6F9-46A1-AA1B-BDD35E2A322D}">
+  <dimension ref="A1:AP29"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="57.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.625" customWidth="1"/>
+    <col min="4" max="42" width="10.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:42">
+      <c r="A1" t="s">
+        <v>826</v>
+      </c>
+      <c r="B1">
+        <v>2020</v>
+      </c>
+      <c r="C1">
+        <v>2021</v>
+      </c>
+      <c r="D1">
+        <v>2022</v>
+      </c>
+      <c r="E1">
+        <v>2023</v>
+      </c>
+      <c r="F1">
+        <v>2024</v>
+      </c>
+      <c r="G1">
+        <v>2025</v>
+      </c>
+      <c r="H1">
+        <v>2026</v>
+      </c>
+      <c r="I1">
+        <v>2027</v>
+      </c>
+      <c r="J1">
+        <v>2028</v>
+      </c>
+      <c r="K1">
+        <v>2029</v>
+      </c>
+      <c r="L1">
+        <v>2030</v>
+      </c>
+      <c r="M1">
+        <v>2031</v>
+      </c>
+      <c r="N1">
+        <v>2032</v>
+      </c>
+      <c r="O1">
+        <v>2033</v>
+      </c>
+      <c r="P1">
+        <v>2034</v>
+      </c>
+      <c r="Q1">
+        <v>2035</v>
+      </c>
+      <c r="R1">
+        <v>2036</v>
+      </c>
+      <c r="S1">
+        <v>2037</v>
+      </c>
+      <c r="T1">
+        <v>2038</v>
+      </c>
+      <c r="U1">
+        <v>2039</v>
+      </c>
+      <c r="V1">
+        <v>2040</v>
+      </c>
+      <c r="W1">
+        <v>2041</v>
+      </c>
+      <c r="X1">
+        <v>2042</v>
+      </c>
+      <c r="Y1">
+        <v>2043</v>
+      </c>
+      <c r="Z1">
+        <v>2044</v>
+      </c>
+      <c r="AA1">
+        <v>2045</v>
+      </c>
+      <c r="AB1">
+        <v>2046</v>
+      </c>
+      <c r="AC1">
+        <v>2047</v>
+      </c>
+      <c r="AD1">
+        <v>2048</v>
+      </c>
+      <c r="AE1">
+        <v>2049</v>
+      </c>
+      <c r="AF1">
+        <v>2050</v>
+      </c>
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="2" spans="1:42">
+      <c r="A2" t="s">
+        <v>827</v>
+      </c>
+      <c r="B2" s="135">
+        <v>-7077360000000</v>
+      </c>
+      <c r="C2" s="135">
+        <v>-7514470000000</v>
+      </c>
+      <c r="D2" s="135">
+        <v>-9145610000000</v>
+      </c>
+      <c r="E2" s="135">
+        <v>-11647600000000</v>
+      </c>
+      <c r="F2" s="135">
+        <v>-13778800000000</v>
+      </c>
+      <c r="G2" s="135">
+        <v>-15434100000000</v>
+      </c>
+      <c r="H2" s="135">
+        <v>-17089300000000</v>
+      </c>
+      <c r="I2" s="135">
+        <v>-18744500000000</v>
+      </c>
+      <c r="J2" s="135">
+        <v>-20399700000000</v>
+      </c>
+      <c r="K2" s="135">
+        <v>-22055000000000</v>
+      </c>
+      <c r="L2" s="135">
+        <v>-23710200000000</v>
+      </c>
+      <c r="M2" s="135">
+        <v>-25365400000000</v>
+      </c>
+      <c r="N2" s="135">
+        <v>-27020600000000</v>
+      </c>
+      <c r="O2" s="135">
+        <v>-28675900000000</v>
+      </c>
+      <c r="P2" s="135">
+        <v>-30331100000000</v>
+      </c>
+      <c r="Q2" s="135">
+        <v>-31986300000000</v>
+      </c>
+      <c r="R2" s="135">
+        <v>-33641500000000</v>
+      </c>
+      <c r="S2" s="135">
+        <v>-35296700000000</v>
+      </c>
+      <c r="T2" s="135">
+        <v>-36952000000000</v>
+      </c>
+      <c r="U2" s="135">
+        <v>-38607200000000</v>
+      </c>
+      <c r="V2" s="135">
+        <v>-40262400000000</v>
+      </c>
+      <c r="W2" s="135">
+        <v>-41917600000000</v>
+      </c>
+      <c r="X2" s="135">
+        <v>-43572900000000</v>
+      </c>
+      <c r="Y2" s="135">
+        <v>-45228100000000</v>
+      </c>
+      <c r="Z2" s="135">
+        <v>-46883300000000</v>
+      </c>
+      <c r="AA2" s="135">
+        <v>-48538500000000</v>
+      </c>
+      <c r="AB2" s="135">
+        <v>-50193800000000</v>
+      </c>
+      <c r="AC2" s="135">
+        <v>-51849000000000</v>
+      </c>
+      <c r="AD2" s="135">
+        <v>-53504200000000</v>
+      </c>
+      <c r="AE2" s="135">
+        <v>-55159400000000</v>
+      </c>
+      <c r="AF2" s="135">
+        <v>-56814600000000</v>
+      </c>
+      <c r="AG2" s="135">
+        <v>-58469900000000</v>
+      </c>
+      <c r="AH2" s="135">
+        <v>-60125100000000</v>
+      </c>
+      <c r="AI2" s="135">
+        <v>-61780300000000</v>
+      </c>
+      <c r="AJ2" s="135">
+        <v>-63435500000000</v>
+      </c>
+      <c r="AK2" s="135">
+        <v>-65090800000000</v>
+      </c>
+      <c r="AL2" s="135">
+        <v>-66746000000000</v>
+      </c>
+      <c r="AM2" s="135">
+        <v>-68401200000000</v>
+      </c>
+      <c r="AN2" s="135">
+        <v>-70056400000000</v>
+      </c>
+      <c r="AO2" s="135">
+        <v>-71711700000000</v>
+      </c>
+      <c r="AP2" s="135">
+        <v>-73366900000000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:42">
+      <c r="A3" t="s">
+        <v>828</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:42">
+      <c r="A4" t="s">
+        <v>829</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:42">
+      <c r="A5" t="s">
+        <v>830</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:42">
+      <c r="A6" t="s">
+        <v>831</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:42">
+      <c r="A7" t="s">
+        <v>832</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:42">
+      <c r="A8" t="s">
+        <v>833</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:42">
+      <c r="A9" t="s">
+        <v>834</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:42">
+      <c r="A10" t="s">
+        <v>835</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:42">
+      <c r="A11" t="s">
+        <v>836</v>
+      </c>
+      <c r="B11" s="135">
+        <v>4699360000</v>
+      </c>
+      <c r="C11" s="135">
+        <v>4989600000</v>
+      </c>
+      <c r="D11" s="135">
+        <v>6072690000</v>
+      </c>
+      <c r="E11" s="135">
+        <v>7734000000</v>
+      </c>
+      <c r="F11" s="135">
+        <v>9149150000</v>
+      </c>
+      <c r="G11" s="135">
+        <v>10248200000</v>
+      </c>
+      <c r="H11" s="135">
+        <v>11347300000</v>
+      </c>
+      <c r="I11" s="135">
+        <v>12446400000</v>
+      </c>
+      <c r="J11" s="135">
+        <v>13545400000</v>
+      </c>
+      <c r="K11" s="135">
+        <v>14644500000</v>
+      </c>
+      <c r="L11" s="135">
+        <v>15743600000</v>
+      </c>
+      <c r="M11" s="135">
+        <v>16842600000</v>
+      </c>
+      <c r="N11" s="135">
+        <v>17941700000</v>
+      </c>
+      <c r="O11" s="135">
+        <v>19040800000</v>
+      </c>
+      <c r="P11" s="135">
+        <v>20139800000</v>
+      </c>
+      <c r="Q11" s="135">
+        <v>21238900000</v>
+      </c>
+      <c r="R11" s="135">
+        <v>22338000000</v>
+      </c>
+      <c r="S11" s="135">
+        <v>23437000000</v>
+      </c>
+      <c r="T11" s="135">
+        <v>24536100000</v>
+      </c>
+      <c r="U11" s="135">
+        <v>25635200000</v>
+      </c>
+      <c r="V11" s="135">
+        <v>26734200000</v>
+      </c>
+      <c r="W11" s="135">
+        <v>27833300000</v>
+      </c>
+      <c r="X11" s="135">
+        <v>28932400000</v>
+      </c>
+      <c r="Y11" s="135">
+        <v>30031400000</v>
+      </c>
+      <c r="Z11" s="135">
+        <v>31130500000</v>
+      </c>
+      <c r="AA11" s="135">
+        <v>32229600000</v>
+      </c>
+      <c r="AB11" s="135">
+        <v>33328700000</v>
+      </c>
+      <c r="AC11" s="135">
+        <v>34427700000</v>
+      </c>
+      <c r="AD11" s="135">
+        <v>35526800000</v>
+      </c>
+      <c r="AE11" s="135">
+        <v>36625900000</v>
+      </c>
+      <c r="AF11" s="135">
+        <v>37724900000</v>
+      </c>
+      <c r="AG11" s="135">
+        <v>38824000000</v>
+      </c>
+      <c r="AH11" s="135">
+        <v>39923100000</v>
+      </c>
+      <c r="AI11" s="135">
+        <v>41022100000</v>
+      </c>
+      <c r="AJ11" s="135">
+        <v>42121200000</v>
+      </c>
+      <c r="AK11" s="135">
+        <v>43220300000</v>
+      </c>
+      <c r="AL11" s="135">
+        <v>44319300000</v>
+      </c>
+      <c r="AM11" s="135">
+        <v>45418400000</v>
+      </c>
+      <c r="AN11" s="135">
+        <v>46517500000</v>
+      </c>
+      <c r="AO11" s="135">
+        <v>47616500000</v>
+      </c>
+      <c r="AP11" s="135">
+        <v>48715600000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:42">
+      <c r="A12" t="s">
+        <v>837</v>
+      </c>
+      <c r="B12" s="135">
+        <v>272478000</v>
+      </c>
+      <c r="C12" s="135">
+        <v>289307000</v>
+      </c>
+      <c r="D12" s="135">
+        <v>352106000</v>
+      </c>
+      <c r="E12" s="135">
+        <v>448432000</v>
+      </c>
+      <c r="F12" s="135">
+        <v>530485000</v>
+      </c>
+      <c r="G12" s="135">
+        <v>594212000</v>
+      </c>
+      <c r="H12" s="135">
+        <v>657938000</v>
+      </c>
+      <c r="I12" s="135">
+        <v>721664000</v>
+      </c>
+      <c r="J12" s="135">
+        <v>785390000</v>
+      </c>
+      <c r="K12" s="135">
+        <v>849116000</v>
+      </c>
+      <c r="L12" s="135">
+        <v>912842000</v>
+      </c>
+      <c r="M12" s="135">
+        <v>976568000</v>
+      </c>
+      <c r="N12" s="135">
+        <v>1040290000</v>
+      </c>
+      <c r="O12" s="135">
+        <v>1104020000</v>
+      </c>
+      <c r="P12" s="135">
+        <v>1167750000</v>
+      </c>
+      <c r="Q12" s="135">
+        <v>1231470000</v>
+      </c>
+      <c r="R12" s="135">
+        <v>1295200000</v>
+      </c>
+      <c r="S12" s="135">
+        <v>1358920000</v>
+      </c>
+      <c r="T12" s="135">
+        <v>1422650000</v>
+      </c>
+      <c r="U12" s="135">
+        <v>1486380000</v>
+      </c>
+      <c r="V12" s="135">
+        <v>1550100000</v>
+      </c>
+      <c r="W12" s="135">
+        <v>1613830000</v>
+      </c>
+      <c r="X12" s="135">
+        <v>1677560000</v>
+      </c>
+      <c r="Y12" s="135">
+        <v>1741280000</v>
+      </c>
+      <c r="Z12" s="135">
+        <v>1805010000</v>
+      </c>
+      <c r="AA12" s="135">
+        <v>1868730000</v>
+      </c>
+      <c r="AB12" s="135">
+        <v>1932460000</v>
+      </c>
+      <c r="AC12" s="135">
+        <v>1996190000</v>
+      </c>
+      <c r="AD12" s="135">
+        <v>2059910000</v>
+      </c>
+      <c r="AE12" s="135">
+        <v>2123640000</v>
+      </c>
+      <c r="AF12" s="135">
+        <v>2187360000</v>
+      </c>
+      <c r="AG12" s="135">
+        <v>2251090000</v>
+      </c>
+      <c r="AH12" s="135">
+        <v>2314820000</v>
+      </c>
+      <c r="AI12" s="135">
+        <v>2378540000</v>
+      </c>
+      <c r="AJ12" s="135">
+        <v>2442270000</v>
+      </c>
+      <c r="AK12" s="135">
+        <v>2505990000</v>
+      </c>
+      <c r="AL12" s="135">
+        <v>2569720000</v>
+      </c>
+      <c r="AM12" s="135">
+        <v>2633450000</v>
+      </c>
+      <c r="AN12" s="135">
+        <v>2697170000</v>
+      </c>
+      <c r="AO12" s="135">
+        <v>2760900000</v>
+      </c>
+      <c r="AP12" s="135">
+        <v>2824620000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:42">
+      <c r="A13" t="s">
+        <v>838</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="29" t="s">
+        <v>335</v>
+      </c>
+      <c r="B17">
+        <v>2020</v>
+      </c>
+      <c r="C17">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="29" t="s">
+        <v>336</v>
+      </c>
+      <c r="B18">
+        <f>温室气体排放清单!N9*10^10</f>
+        <v>-1342629000000000</v>
+      </c>
+      <c r="C18">
+        <f>温室气体排放清单!Q9*10^10</f>
+        <v>-1346499000000000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="29" t="s">
+        <v>337</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="29" t="s">
+        <v>338</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="29" t="s">
+        <v>339</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="29" t="s">
+        <v>341</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="29" t="s">
+        <v>342</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="29" t="s">
+        <v>343</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="29" t="s">
+        <v>344</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="29" t="s">
+        <v>345</v>
+      </c>
+      <c r="B27">
+        <f>温室气体排放清单!O9*10^10</f>
+        <v>1398000000000</v>
+      </c>
+      <c r="C27">
+        <f>温室气体排放清单!R9*10^10</f>
+        <v>1110000000000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="29" t="s">
+        <v>347</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="33" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
@@ -5548,169 +7425,169 @@
       <c r="A2" s="29" t="s">
         <v>336</v>
       </c>
-      <c r="B2">
-        <f>温室气体排放清单!N9*10^10</f>
-        <v>-1342629000000000</v>
-      </c>
-      <c r="C2">
-        <f>温室气体排放清单!Q9*10^10</f>
-        <v>-1346499000000000</v>
+      <c r="B2" s="135">
+        <f>'Policy Action'!B18-'Policy Action'!B2</f>
+        <v>-1335551640000000</v>
+      </c>
+      <c r="C2" s="135">
+        <f>'Policy Action'!C18-'Policy Action'!C2</f>
+        <v>-1338984530000000</v>
       </c>
       <c r="D2">
         <f>C2</f>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="E2">
         <f t="shared" ref="E2:AP2" si="0">D2</f>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="F2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="G2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="H2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="I2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="J2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="K2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="L2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="M2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="N2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="Q2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="S2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="T2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="U2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="V2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="W2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="X2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="Y2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="Z2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="AA2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="AB2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="AC2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="AD2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="AE2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="AF2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="AG2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="AH2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="AI2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="AJ2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="AK2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="AL2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="AM2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="AN2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="AO2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
       <c r="AP2">
         <f t="shared" si="0"/>
-        <v>-1346499000000000</v>
+        <v>-1338984530000000</v>
       </c>
     </row>
     <row r="3" spans="1:42">
@@ -6741,169 +8618,169 @@
       <c r="A11" s="29" t="s">
         <v>345</v>
       </c>
-      <c r="B11">
-        <f>温室气体排放清单!O9*10^10</f>
-        <v>1398000000000</v>
-      </c>
-      <c r="C11">
-        <f>温室气体排放清单!R9*10^10</f>
-        <v>1110000000000</v>
+      <c r="B11" s="135">
+        <f>'Policy Action'!B27-'Policy Action'!B2</f>
+        <v>8475360000000</v>
+      </c>
+      <c r="C11" s="135">
+        <f>'Policy Action'!C27-'Policy Action'!C2</f>
+        <v>8624470000000</v>
       </c>
       <c r="D11">
         <f>C11</f>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="E11">
         <f t="shared" ref="E11:AP11" si="1">D11</f>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="F11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="G11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="H11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="I11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="J11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="K11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="L11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="M11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="N11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="O11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="P11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="Q11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="R11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="S11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="T11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="U11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="V11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="W11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="X11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="Y11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="Z11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="AA11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="AB11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="AC11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="AD11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="AE11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="AF11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="AG11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="AH11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="AI11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="AJ11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="AK11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="AL11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="AM11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="AN11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="AO11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
       <c r="AP11">
         <f t="shared" si="1"/>
-        <v>1110000000000</v>
+        <v>8624470000000</v>
       </c>
     </row>
     <row r="12" spans="1:42">
@@ -6915,163 +8792,163 @@
       </c>
       <c r="C12">
         <f>-'data from RPEPUACE'!B12*(C2-$B2)+B12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="D12">
         <f>-'data from RPEPUACE'!C12*(D2-$B2)+C12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="E12">
         <f>-'data from RPEPUACE'!D12*(E2-$B2)+D12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="F12">
         <f>-'data from RPEPUACE'!E12*(F2-$B2)+E12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="G12">
         <f>-'data from RPEPUACE'!F12*(G2-$B2)+F12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="H12">
         <f>-'data from RPEPUACE'!G12*(H2-$B2)+G12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="I12">
         <f>-'data from RPEPUACE'!H12*(I2-$B2)+H12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="J12">
         <f>-'data from RPEPUACE'!I12*(J2-$B2)+I12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="K12">
         <f>-'data from RPEPUACE'!J12*(K2-$B2)+J12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="L12">
         <f>-'data from RPEPUACE'!K12*(L2-$B2)+K12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="M12">
         <f>-'data from RPEPUACE'!L12*(M2-$B2)+L12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="N12">
         <f>-'data from RPEPUACE'!M12*(N2-$B2)+M12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="O12">
         <f>-'data from RPEPUACE'!N12*(O2-$B2)+N12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="P12">
         <f>-'data from RPEPUACE'!O12*(P2-$B2)+O12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="Q12">
         <f>-'data from RPEPUACE'!P12*(Q2-$B2)+P12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="R12">
         <f>-'data from RPEPUACE'!Q12*(R2-$B2)+Q12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="S12">
         <f>-'data from RPEPUACE'!R12*(S2-$B2)+R12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="T12">
         <f>-'data from RPEPUACE'!S12*(T2-$B2)+S12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="U12">
         <f>-'data from RPEPUACE'!T12*(U2-$B2)+T12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="V12">
         <f>-'data from RPEPUACE'!U12*(V2-$B2)+U12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="W12">
         <f>-'data from RPEPUACE'!V12*(W2-$B2)+V12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="X12">
         <f>-'data from RPEPUACE'!W12*(X2-$B2)+W12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="Y12">
         <f>-'data from RPEPUACE'!X12*(Y2-$B2)+X12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="Z12">
         <f>-'data from RPEPUACE'!Y12*(Z2-$B2)+Y12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="AA12">
         <f>-'data from RPEPUACE'!Z12*(AA2-$B2)+Z12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="AB12">
         <f>-'data from RPEPUACE'!AA12*(AB2-$B2)+AA12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="AC12">
         <f>-'data from RPEPUACE'!AB12*(AC2-$B2)+AB12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="AD12">
         <f>-'data from RPEPUACE'!AC12*(AD2-$B2)+AC12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="AE12">
         <f>-'data from RPEPUACE'!AD12*(AE2-$B2)+AD12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="AF12">
         <f>-'data from RPEPUACE'!AE12*(AF2-$B2)+AE12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="AG12">
         <f>-'data from RPEPUACE'!AF12*(AG2-$B2)+AF12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="AH12">
         <f>-'data from RPEPUACE'!AG12*(AH2-$B2)+AG12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="AI12">
         <f>-'data from RPEPUACE'!AH12*(AI2-$B2)+AH12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="AJ12">
         <f>-'data from RPEPUACE'!AI12*(AJ2-$B2)+AI12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="AK12">
         <f>-'data from RPEPUACE'!AJ12*(AK2-$B2)+AJ12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="AL12">
         <f>-'data from RPEPUACE'!AK12*(AL2-$B2)+AK12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="AM12">
         <f>-'data from RPEPUACE'!AL12*(AM2-$B2)+AL12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="AN12">
         <f>-'data from RPEPUACE'!AM12*(AN2-$B2)+AM12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="AO12">
         <f>-'data from RPEPUACE'!AN12*(AO2-$B2)+AN12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
       <c r="AP12">
         <f>-'data from RPEPUACE'!AO12*(AP2-$B2)+AO12</f>
-        <v>149108565.87285522</v>
+        <v>132267003.79825994</v>
       </c>
     </row>
     <row r="13" spans="1:42">
